--- a/www/download/COUNTRY.DNK.EXI382.xlsx
+++ b/www/download/COUNTRY.DNK.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Dinamarca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1211</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2.648</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2.715</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2.739</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2.588</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2.813</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2.814</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2.827</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2.845</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2.856</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2.695</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2.915</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2.913</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2.848</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2.732</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2.703</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2.698</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>2.684</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.746</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>2.891</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2.792</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2.789</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2.791</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2.569</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2.533</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2.54</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2.388</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.456</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2.484</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2.327</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2.084</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.553</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.558</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.578</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.593</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.552</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.603</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2.441</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2.653</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2.651</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2.597</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2.475</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.457</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.453</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.438</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.483</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2.617</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2.523</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2.513</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2.509</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2.331</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2.283</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2.311</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4999.609</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4921.162</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4931.688</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4748.265</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4247.673</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>5283.839</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5099.731</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5178.395</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>5281.112</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>5096.332</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5122.786</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>5015.492</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>5403.361</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>5410.806</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>5241.104</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>4974.992</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>4958.534</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>4969.841</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>4920.642</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>5035.135</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>5315.74</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5139.539</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>5155.566</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>5183.932</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>4811.529</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>4755.058</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>4757.086</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4874.13</t>
+          <t>11347243802.0056</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4526.904</t>
+          <t>10185575128.589</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4543.232</t>
+          <t>9117087456.9485</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4332.852</t>
+          <t>9647486813.60862</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3859.281</t>
+          <t>7936078396.51795</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4943.423</t>
+          <t>9969788206.43244</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4735.495</t>
+          <t>9821488654.07882</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4857.539</t>
+          <t>9494648089.62866</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4920.819</t>
+          <t>9595074605.42514</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4799.586</t>
+          <t>9769957422.58156</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4808.336</t>
+          <t>10808838412.7097</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4751.638</t>
+          <t>10916207460.6465</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5265.187</t>
+          <t>10489763979.6777</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5277.768</t>
+          <t>13824545780.1537</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5106.672</t>
+          <t>11118338167.3919</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>4843.766</t>
+          <t>10593580919.9581</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>4831.166</t>
+          <t>13104101527.3097</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4830.285</t>
+          <t>11233542306.1187</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>4785.396</t>
+          <t>11654984976.1723</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>4900.88</t>
+          <t>9589143452.08831</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>5179.014</t>
+          <t>9261388443.82494</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>5006.276</t>
+          <t>9694712711.48961</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>5020.564</t>
+          <t>9156567471.94128</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5046.368</t>
+          <t>9347344965.22329</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4689.262</t>
+          <t>9326901602.60039</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>4625.921</t>
+          <t>8917244414.35239</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4638.435</t>
+          <t>9505306468.76743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4750945569.38142</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3745419257.85153</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3494090385.99184</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3106573424.30458</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3468273690.67135</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4409582392.21969</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4394606235.88136</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4494720214.14895</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>4511692541.1622</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4220200512.4629</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4479153238.56729</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4395892625.98453</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3933665296.12482</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4344828492.27929</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4169526375.38894</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3704786178.25984</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4123368355.09031</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3826359850.65624</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4486373401.66431</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3899094121.75341</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>3738258279.04179</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3910061966.46955</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3775338541.88911</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>4307642113.76112</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3419979402.46498</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>4018141176.37169</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3983946062.55775</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4767022507.27923</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7512013.8898281</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>7994373.32887386</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2392498790.91566</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5905750.88146707</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7585459.09130902</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>328591993.456279</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5418660.36271002</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6195037.96540457</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>23251838.3077343</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>389596806.228811</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4411401.90804211</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4250549.63571471</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>325823444.544069</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>8321024.15372588</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3744690.04788786</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4256353.90433584</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4463785.41152209</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4382866.06811586</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>20898210.5796315</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>23906713.3537579</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>20846018.791584</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>417857957353.651</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14090416.2905815</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>18778589.9711683</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15386100.8449739</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>15473801.5274917</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11316.5046867342</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22584.6311331718</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>24537.203781469</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>22741.9089532555</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>19851.8277476391</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>33540.8397950222</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>32226.1060666235</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>31548.3511311022</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>29323.7519333099</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>27707.1180555696</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>30402.579085301</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>33407.250840142</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>34615.5352915641</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>35268.5866555913</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>34267.6099373719</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>36287.6262910923</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>38142.80408791</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>42819.0219643764</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>41618.165537241</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>41624.0535410058</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>50655.3758643541</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>43290.184822476</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>45897.2558287778</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>45527.346087975</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>46789.1007847658</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>41852.9814976651</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>45066.9134480384</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>42298.0159705147</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>77400.9231395595</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>75458.7050281388</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>82089.8962967218</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>71228.6435336658</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>106963.997997256</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>105804.456454119</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>99149.1606860875</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>92043.4546578579</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>91587.7017348133</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>108626.359217818</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>117352.613149916</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>116834.069672626</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>154717.535828209</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>124693.8203154</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>137010.592929974</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>176437.695315738</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>166945.59401656</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>169195.175044535</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>144088.759762558</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>157204.170156024</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>149991.144418033</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>149774.80417163</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>148701.813908083</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>158089.776534862</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>143785.724289739</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>150475.276434889</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.0259283506171146</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.208650804715549</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.300261727119119</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.394736710905225</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.112738308507907</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.121063756223605</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0775697614891324</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0807211057784072</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.0906813695982631</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.137288540694706</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0734920747364585</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0809267660250803</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.338493899109025</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.214724127633531</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.224760689881261</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.307434698505566</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.171655206122402</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.262370814175254</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.0666512952810134</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.256927925461641</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.38540817944231</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.280357276038921</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.329831511868251</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.171492039620943</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.371137484895559</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.151258852608663</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.164281632393802</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1989.77660032023</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1525.13203756462</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1406.41216631458</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1334.89748380269</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1664.07911461047</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1727.21597815096</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1718.25392394517</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1743.62643112287</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1739.7495627815</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1653.61878941441</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1720.83185622477</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1800.63598328062</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1482.77933436035</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1639.06311010988</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1605.82567894788</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1497.0042743894</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1678.55418485249</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1559.93307947942</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1840.11049656038</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1570.20937418164</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1428.62772115495</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1549.5516100861</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1502.16043853413</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1716.55858695775</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1467.48626794814</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1760.14687766593</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1723.60166888143</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>9686355969.52514</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>5425013714.91502</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>4398771934.03227</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>4448313249.37498</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>5577055534.12415</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>6222761996.34788</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>6581828213.36259</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>6495586521.3895</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>6958834299.97931</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>7126282472.87267</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>6893300251.70248</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>6342278803.77426</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>5056200867.60476</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>5724535454.74444</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>5753341641.37984</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>6225616588.48693</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>6226658685.78116</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>5818561166.24613</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>6224584517.56102</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>5625396379.74732</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>5422206128.07466</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>5962002423.05289</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>5643698378.8145</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>5717280407.32611</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>6063122184.6618</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>6659658805.84833</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>6245845259.83222</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>9092905344.70659</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5086768097.41863</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3912647153.76357</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4255889718.07419</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5177044536.18717</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5810675051.77663</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6044215271.27929</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6068705035.87232</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>6287620524.07038</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6584592854.39276</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6383994790.87138</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5880004104.26535</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>4737783316.33478</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>5249501027.6641</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>5201905310.12419</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5458523753.35277</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5543875733.18593</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>5071496029.65257</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>5430754122.01227</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>4769208561.43171</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>4378130341.29115</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>4939299258.52997</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>4709541088.63228</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>4722347264.55098</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>4911581144.98302</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>5513310230.29251</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>6108569708.33807</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>593450624.818549</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>338245617.496395</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>486124780.268695</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>192423531.300782</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>400010997.936979</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>412086944.57125</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>537612942.083306</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>426881485.517181</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>671213775.90893</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>541689618.479913</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>509305460.831101</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>462274699.508911</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>318417551.26998</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>475034427.080338</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>551436331.255652</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>767092835.134157</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>682782952.595224</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>747065136.593556</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>793830395.548753</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>856187818.315609</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1044075786.78351</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>1022703164.52292</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>934157290.182216</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>994933142.775136</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1151541039.67878</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1146348575.55581</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>137275551.494152</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>2041.36822566306</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1843.35206449994</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>1828.70391241354</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>1861.83052595462</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1851.68457921499</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>1936.31923227534</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>1851.53847100337</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>1884.37388470756</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>1897.51243589251</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>1880.64169987846</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>1847.29935961132</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>1946.35563019591</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>1984.69109276627</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>1991.00950656452</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>1966.75216637725</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>1957.23533214785</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>1966.68674944096</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>1969.21399160135</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>1962.75624461632</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1973.64001123055</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1979.23253026609</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>1983.97967857157</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>1997.62028704452</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>2010.93472016398</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>2012.12543055318</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>2026.3846748044</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>2006.75776464195</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>1887.93858034814</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1812.78299627904</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1800.60900361465</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1834.5110690421</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1815.32244967736</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>1878.16407777306</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1811.94919168614</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>1832.08738722771</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1856.40888638919</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>1813.70582583096</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1793.94382966801</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1860.75981301383</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>1853.44938771308</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>1857.65990318302</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>1840.33989957466</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>1820.74074074062</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>1834.38792497565</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1841.90979171274</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>1833.66573504721</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1833.71220392407</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>1838.57755770497</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>1840.89054435497</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1848.60836165078</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>1857.43328725482</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>1872.69468840554</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>1877.1623150135</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>1872.73484557456</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>44836.8672713826</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>45733.4923630941</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>49998.9445430014</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>49935.3951113782</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>59238.0278965106</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>77351.7596938609</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>82297.7064467773</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>83705.703794594</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>77061.7315609676</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>75916.2489155185</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>87111.9052818047</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>94070.0338733657</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>92685.2688298824</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>98156.9823036796</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>86604.120136522</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>102535.665652016</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>108591.240338601</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>118182.80956504</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>119546.870315092</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>122075.686639902</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>136060.416076341</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>136468.487628598</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>149765.592013677</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>156920.281389104</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>172983.404783232</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>178547.698160969</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>181464.804587098</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2264117166.07818</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2036106907.05693</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1842636232.567</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2072440113.44949</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2066979279.98403</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2673345510.62639</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2688012775.97589</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2541381838.88322</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2346952397.97333</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2161296689.22269</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2678552714.09067</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2514876767.49174</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2359667739.71708</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>3018664082.34391</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>2354581486.16138</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>2526386273.30062</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>3100659096.09337</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2738998092.82175</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2912400488.27708</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2373682073.46611</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2395266511.05308</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2482602968.10736</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2445909574.89187</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2670648418.15168</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2785060909.82197</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3032192156.49616</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3138962755.45538</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>36124.1209982056</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>34786.3745509285</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>41277.1477885068</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>43587.6966583605</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>46134.4138553516</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>61750.9019015135</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>65112.6079773938</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>66774.6290500432</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>59925.5076437061</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>60983.9862977242</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>71806.6806451771</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>82007.237305338</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>83852.7668424895</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>87084.8269582206</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>73056.6006136147</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>80468.8333677408</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>87921.3802999831</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>98132.8509606233</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>97188.1899952153</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>97878.3634247349</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>111838.830974528</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>111740.846521858</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>122173.479806098</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>133684.429780027</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>142917.53453583</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>148015.695287784</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>150886.650718825</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4999.609</t>
+          <t>7014473752.0142</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4921.162</t>
+          <t>5237344469.43982</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4931.688</t>
+          <t>4608794942.35969</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4748.265</t>
+          <t>5324857635.06723</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4247.673</t>
+          <t>5240256843.91187</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5283.839</t>
+          <t>6475781405.83015</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5099.731</t>
+          <t>6498245689.92427</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5178.395</t>
+          <t>6203831505.28627</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5281.112</t>
+          <t>6394725127.45868</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5096.332</t>
+          <t>6549153885.14661</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>5122.786</t>
+          <t>7012045202.21855</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>5015.492</t>
+          <t>7062311568.0513</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>5403.361</t>
+          <t>6319027277.03318</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>5410.806</t>
+          <t>7225878571.5688</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5241.104</t>
+          <t>6113844627.17388</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>4974.992</t>
+          <t>6031117945.91227</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>4958.534</t>
+          <t>6943757259.43173</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>4969.841</t>
+          <t>6371487580.00299</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>4920.642</t>
+          <t>6575718649.66165</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>5035.135</t>
+          <t>5426755572.24398</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>5315.74</t>
+          <t>5476095939.44409</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>5139.539</t>
+          <t>5822077537.24278</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>5155.566</t>
+          <t>5431859633.7827</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>5183.932</t>
+          <t>6078524361.79277</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>4811.529</t>
+          <t>6104149104.9372</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>4755.058</t>
+          <t>6728984905.05255</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>4757.086</t>
+          <t>6405423330.7795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4874.13</t>
+          <t>8712.74627317697</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4526.904</t>
+          <t>10947.1178121656</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4543.232</t>
+          <t>8721.79675449462</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4332.852</t>
+          <t>6347.69845301772</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3859.281</t>
+          <t>13103.614041159</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4943.423</t>
+          <t>15600.8577923474</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4735.495</t>
+          <t>17185.0984693835</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4857.539</t>
+          <t>16931.0747445508</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4920.819</t>
+          <t>17136.2239172615</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4799.586</t>
+          <t>14932.2626177943</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>4808.336</t>
+          <t>15305.2246366276</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4751.638</t>
+          <t>12062.7965680277</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5265.187</t>
+          <t>8832.50198739286</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5277.768</t>
+          <t>11072.155345459</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5106.672</t>
+          <t>13547.5195229073</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>4843.766</t>
+          <t>22066.8322842755</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>4831.166</t>
+          <t>20669.860038618</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>4830.285</t>
+          <t>20049.9586044169</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>4785.396</t>
+          <t>22358.6803198766</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>4900.88</t>
+          <t>24197.3232151668</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>5179.014</t>
+          <t>24221.5851018129</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>5006.276</t>
+          <t>24727.6411067404</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>5020.564</t>
+          <t>27592.1122075783</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5046.368</t>
+          <t>23235.851609077</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>4689.262</t>
+          <t>30065.8702474015</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>4625.921</t>
+          <t>30532.0028731859</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>4638.435</t>
+          <t>30578.1538682729</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7820.256</t>
+          <t>-4750356585.93602</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7343.619</t>
+          <t>-3201237562.38289</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6675.148</t>
+          <t>-2766158709.79269</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7000.992</t>
+          <t>-3252417521.61774</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>5767.837</t>
+          <t>-3173277563.92783</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7300.397</t>
+          <t>-3802435895.20376</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>7180.696</t>
+          <t>-3810232913.94838</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6989.676</t>
+          <t>-3662449666.40305</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7059.484</t>
+          <t>-4047772729.48535</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7123.363</t>
+          <t>-4387857195.92392</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>7823.694</t>
+          <t>-4333492488.12788</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>7867.993</t>
+          <t>-4547434800.55957</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7612.37</t>
+          <t>-3959359537.3161</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>9523.602</t>
+          <t>-4207214489.22489</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7916.436</t>
+          <t>-3759263141.01251</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>7467.232</t>
+          <t>-3504731672.61165</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>8881.99</t>
+          <t>-3843098163.33836</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>7843.244</t>
+          <t>-3632489487.18124</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>8117.834</t>
+          <t>-3663318161.38457</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6850.945</t>
+          <t>-3053073498.77786</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>6739.838</t>
+          <t>-3080829428.39102</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>6962.018</t>
+          <t>-3339474569.13542</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>6647.357</t>
+          <t>-2985950058.89084</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6786.448</t>
+          <t>-3407875943.64109</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>6774.986</t>
+          <t>-3319088195.11523</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>6452.9</t>
+          <t>-3696792748.55639</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>6830.771</t>
+          <t>-3266460575.32413</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>55329.8970591669</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>60409.3937276343</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>52517.8967869409</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>53048.5624864453</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>68431.3106893785</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>71494.6395533472</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>72733.9762554518</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>77314.6290141188</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>79105.6528092405</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>78815.6050054962</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>89189.7055657537</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>88398.9979645355</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>94538.865236406</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93982.0621221915</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>89856.4711757898</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>95999.0730144364</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>97047.0847540052</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>101768.021312357</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102311.584547471</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>108460.100015024</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>109026.110441887</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>113768.264467546</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>119264.504895331</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>108557.893248899</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>92382.6293842846</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>134380.205687479</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>131565.184017464</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>3035.867</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2972.025</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2964.639</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2672.707</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2211.83</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>3126.239</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2991.446</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>3021.11</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>3056.856</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>2955.608</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3025.201</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3107.562</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>3107.902</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>3151.37</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>3055.475</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2805.739</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>2832.882</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>2881.234</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>2866.861</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>2770.091</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>2984.266</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2798.071</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2805.955</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>2861.833</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2760.44</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>2595.621</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>2846.812</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>89816.4622472036</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>92825.5722034932</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>94911.5320695377</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>95540.0618419792</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>108397.352776446</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>117754.334584164</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>121396.863132412</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>127198.223822843</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>129934.947954409</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>133533.801667309</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>137563.502039762</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>149206.569886388</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>159718.018372517</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>163746.021693138</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>160373.795248516</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>162713.488159464</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>164808.764808818</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>168487.746165714</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>182515.604755083</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>189737.04462506</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>196071.13713157</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>204400.617544806</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>213104.181860846</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>194165.338842966</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>186559.23122037</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>216565.125251845</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>230204.257044796</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4102.135</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>3271.093</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>3140.977</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2768.512</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>3126.27</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>4009.67</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>3994.488</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>4106.462</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>4171.182</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>3856.362</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>4135.36</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>4051.702</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>3647.84</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>3885.525</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>3756.789</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>3357.834</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>3675.099</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>3446.476</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>4056.014</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>3628.811</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>3473.916</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>3613.965</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>3518.306</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>4030.027</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>3190.265</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>3741.769</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>3657.283</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>18.82</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>38.39</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>44.64</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>23.29</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>18.55</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>18.29</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>17.97</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>24.46</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>16.27</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>17.28</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>44.34</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>35.83</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>35.93</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>44.25</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>31.46</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>40.15</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>17.98</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>35.05</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>49.08</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>38.53</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>46.99</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>23.63</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>26.83</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>5342.036</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.131</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>7.785</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2681.19</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5.774</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>7.523</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>367.518</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>5.163</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6.054</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>25.239</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>435.885</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.19</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.073</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>364.461</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>8.524</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.498</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.937</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>4.147</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>4.111</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>22.613</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>26.062</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>22.702</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>468460.147</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15.325</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>20.602</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16.801</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>16.862</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>62511.832377951</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>65748.151014091</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>68473.3341923988</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>71651.9966521724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>69004.4061704701</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>72645.5575343374</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>74914.5372941276</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>73790.2134956812</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>74951.5788059662</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>81241.4283217904</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>86991.750739228</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>89338.8029561966</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>87564.5279943928</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>91405.5185163799</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>84355.2879445538</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>93500.3415035243</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>95351.6278996067</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>98378.0545920027</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>89822.7149315945</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>89959.2824635267</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>90312.494145014</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>92227.6181072502</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>95399.2842543252</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>117949.582801488</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>133014.599667679</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>114615.255260256</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>108796.284632555</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4874129751.86717</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4526903999.99936</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4543232000.00006</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4332852000.00016</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3859281000.00012</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4943422999.99928</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4735494793.43733</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4857538999.99961</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4920819000.00106</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>4799585682.25798</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4808335503.13213</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>4751637999.99896</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5265186999.99996</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5277768000.00128</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5106671999.99947</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>4843766000.00074</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>4831166000.00193</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>4830285000.00042</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>4785395999.99953</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>4900880285.63519</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>5179013596.65242</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5006276288.53234</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>5020564160.97487</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>5046368445.80708</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>4689261956.29045</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>4625920600.32929</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>4638435225.0836</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4999609451.39184</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>4921161999.99928</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>4931687999.99992</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4748265000.00036</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>4247673000.00013</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5283838999.99931</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5099730999.99973</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5178394999.99954</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5281112000.00102</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5096332000.00074</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5122785999.99976</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5015491999.99899</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>5403361000.00005</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>5410806000.00122</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5241103999.99949</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>4974992000.00079</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>4958534000.00192</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>4969841000.00048</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>4920641999.9995</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>5035134751.20105</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>5315739973.40009</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>5139538902.14448</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>5155566113.50021</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>5183932354.49102</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>4811528777.06346</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>4755058091.5443</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4757086444.44758</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3035866688.31997</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2972024723.05939</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2964639172.39501</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2672707320.15265</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2211830150.11329</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3126239438.34664</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2991446161.20905</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3021109707.08283</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>3056856009.55513</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2955608215.70939</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3025200945.96657</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3107561656.04062</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>3107901627.12091</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3151369934.96923</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3055475199.23828</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>2805738573.10699</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>2832882034.70244</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2881233838.94597</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2866861268.028</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2770091304.27553</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2984266334.55156</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2798071224.20178</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2805954727.14869</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>2861833343.19286</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2760439976.94833</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>2595621139.21682</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>2846812008.41906</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2648184.37603511</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2714700.00000031</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2738899.99999986</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2588299.99999929</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2339900.00000004</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2813300.00000019</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2814499.99999949</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2826500.00000022</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2844800.00000057</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2809899.99999908</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2855599.99999988</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2695400.0000008</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2915300.00000006</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2912700.00000002</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2847900.00000044</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2732400.00000062</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>2703100.00000014</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>2698200.00000064</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2683500.00000017</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2745869.68468992</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2891224.22446814</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2791876.41976038</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2788890.40017992</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>2790911.73290675</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2569307.64360747</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>2533109.71220414</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2540181.51885677</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2387677.87731387</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2455800.00000022</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2484399.99999993</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2327199.99999923</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2084200.00000013</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2553000.00000017</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2557599.99999953</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2577800.00000024</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2593300.00000053</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2552099.99999902</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2602899.9999999</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2441300.00000086</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2652900.00000017</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2650800.00000002</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2596500.00000047</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2474800.00000063</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2456500.0000001</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2452900.00000075</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2438100.00000024</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2483168.28689519</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2616677.68564623</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2523350.58801448</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2513272.51406862</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>2509464.07916989</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2330501.80922431</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>2282844.24860043</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2311407.63813673</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4999609451.39184</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4921161999.99928</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4931687999.99992</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4748265000.00036</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4247673000.00013</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5283838999.99931</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5099730999.99973</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5178394999.99954</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5281112000.00102</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5096332000.00074</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5122785999.99976</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5015491999.99899</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>5403361000.00005</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>5410806000.00122</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>5241103999.99949</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>4974992000.00079</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>4958534000.00192</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>4969841000.00048</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>4920641999.9995</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>5035134751.20105</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>5315739973.40009</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>5139538902.14448</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>5155566113.50021</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>5183932354.49102</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>4811528777.06346</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>4755058091.5443</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>4757086444.44758</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4874129751.86717</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4526903999.99936</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4543232000.00006</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4332852000.00016</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3859281000.00012</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4943422999.99928</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4735494793.43733</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4857538999.99961</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4920819000.00106</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4799585682.25798</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4808335503.13213</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4751637999.99896</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5265186999.99996</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5277768000.00128</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5106671999.99947</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>4843766000.00074</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>4831166000.00193</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>4830285000.00042</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>4785395999.99953</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>4900880285.63519</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>5179013596.65242</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>5006276288.53234</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>5020564160.97487</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>5046368445.80708</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>4689261956.29045</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>4625920600.32929</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>4638435225.0836</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>263288.91572914</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>274819.785106647</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>285859.10654421</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>293860.461816684</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>306749.317590544</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>343050.257643977</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>356873.443824914</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>368665.044278374</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>368662.828535107</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>386221.2128344</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>418385.127158003</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>452176.133153141</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>474422.269767102</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>492476.042175243</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>441324.362877105</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>479976.621642326</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>490080.267783903</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>510479.579959017</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>510794.327958972</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>538283.593744348</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>552930.754579209</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>573706.492309115</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>593533.23020223</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>612891.858543039</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>642762.389516385</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>624360.805005696</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>636272.368509847</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>96060.4446752403</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>99925.4032742949</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>103091.209702738</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>105339.299944049</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>118193.632245162</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>126615.405654907</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>131368.701216377</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>137998.617763696</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>141198.007553517</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>145317.257887552</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>151328.163021267</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>163244.369496257</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>173730.973966957</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>177938.161147552</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>173850.883858995</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>178800.320239999</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>181704.405426361</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>187087.87920909</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>200210.004509508</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>207926.424878804</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>215525.038888096</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>224905.123828361</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>234193.461282825</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>220829.085465618</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>217590.100410967</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>242668.464354967</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>254643.4334717</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
